--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513662_FASEFINALBFFB3_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513662_FASEFINALBFFB3_PROCESSED.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>P. LOPEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4932</v>
+        <v>1.8277</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2798</v>
+        <v>0.2444</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2133</v>
+        <v>1.5832</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2206</v>
+        <v>0.7171</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7389</v>
+        <v>0.1093</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9595</v>
+        <v>0.6079</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4441</v>
+        <v>0.7972</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3952</v>
+        <v>0.1565</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0489</v>
+        <v>0.6407</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2235</v>
+        <v>-0.0801</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1342</v>
+        <v>-0.0473</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9106</v>
+        <v>-0.0328</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1684</v>
+        <v>2.1421</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1684</v>
+        <v>2.1421</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4421</v>
+        <v>-1.0316</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2252</v>
+        <v>-0.5528</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2169</v>
+        <v>-0.4788</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6621</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4563</v>
+        <v>1.7165</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.475</v>
+        <v>0.7814</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9313</v>
+        <v>0.9351</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9907</v>
+        <v>0.2206</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9537</v>
+        <v>-0.7389</v>
       </c>
       <c r="I3" t="n">
-        <v>1.037</v>
+        <v>0.9595</v>
       </c>
       <c r="J3" t="n">
-        <v>3.751</v>
+        <v>0.4441</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9405</v>
+        <v>0.3952</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8105</v>
+        <v>0.0489</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2397</v>
+        <v>-0.2235</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0132</v>
+        <v>-1.1342</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2264</v>
+        <v>0.9106</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.1421</v>
+        <v>1.1684</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.8684</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7263</v>
+        <v>1.1684</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8872</v>
+        <v>-0.3346</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6424</v>
+        <v>-0.2732</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2448</v>
+        <v>-0.0614</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2795</v>
+        <v>0.6621</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2795</v>
+        <v>0.0516</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. LOPEZ DOMINGUEZ</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6907</v>
+        <v>1.2099</v>
       </c>
       <c r="E4" t="n">
-        <v>0.358</v>
+        <v>-1.2484</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3328</v>
+        <v>2.4583</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7171</v>
+        <v>3.9907</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1093</v>
+        <v>2.9537</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6079</v>
+        <v>1.037</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7972</v>
+        <v>3.751</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1565</v>
+        <v>2.9405</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6407</v>
+        <v>0.8105</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0801</v>
+        <v>0.2397</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0473</v>
+        <v>0.0132</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0328</v>
+        <v>0.2264</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1421</v>
+        <v>-2.1421</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.8684</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1421</v>
+        <v>2.7263</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1685</v>
+        <v>-0.3593</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4393</v>
+        <v>-0.131</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7292</v>
+        <v>-0.2282</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SAEZ CALABUIG</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5268</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3735</v>
+        <v>1.1786</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8467</v>
+        <v>-1.2448</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3378</v>
+        <v>-1.1614</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0956</v>
+        <v>0.3458</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4333</v>
+        <v>-1.5072</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8252</v>
+        <v>1.045</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7442</v>
+        <v>2.3734</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08110000000000001</v>
+        <v>-1.3284</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.163</v>
+        <v>-2.2064</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3514</v>
+        <v>-2.0276</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5144</v>
+        <v>-0.1788</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.9474</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5579</v>
+        <v>2.921</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1111</v>
+        <v>-1.4111</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-0.6728</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4518</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6621</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6621</v>
+        <v>1.78</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2211</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>F. GOMEZ CARBONELL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6798</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9174</v>
+        <v>0.6105</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5972</v>
+        <v>-1.1392</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1614</v>
+        <v>-0.4103</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3458</v>
+        <v>-2.9116</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5072</v>
+        <v>2.5013</v>
       </c>
       <c r="J6" t="n">
-        <v>1.045</v>
+        <v>1.287</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3734</v>
+        <v>-0.5695</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3284</v>
+        <v>1.8565</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2064</v>
+        <v>-1.6973</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0276</v>
+        <v>-2.3421</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1788</v>
+        <v>0.6448</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9474</v>
+        <v>1.7526</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.921</v>
+        <v>1.7526</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0248</v>
+        <v>-1.2605</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.6765</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0908</v>
+        <v>-0.584</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5590000000000001</v>
+        <v>-0.6105</v>
       </c>
       <c r="W6" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2211</v>
+        <v>-0.6105</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F. GOMEZ CARBONELL</t>
+          <t>A. SAEZ CALABUIG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3393</v>
+        <v>-0.7927</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0503</v>
+        <v>-1.2499</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3896</v>
+        <v>0.4572</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4103</v>
+        <v>-0.3378</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9116</v>
+        <v>1.0956</v>
       </c>
       <c r="I7" t="n">
-        <v>2.5013</v>
+        <v>-1.4333</v>
       </c>
       <c r="J7" t="n">
-        <v>1.287</v>
+        <v>0.8252</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5695</v>
+        <v>0.7442</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8565</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6973</v>
+        <v>-1.163</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.3421</v>
+        <v>0.3514</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6448</v>
+        <v>-1.5144</v>
       </c>
       <c r="P7" t="n">
-        <v>1.7526</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7526</v>
+        <v>1.5579</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0711</v>
+        <v>-0.377</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2367</v>
+        <v>-0.4393</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8344</v>
+        <v>0.0623</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6105</v>
+        <v>-0.6621</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.6621</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.708</v>
+        <v>-1.2699</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5574</v>
+        <v>-1.2583</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1507</v>
+        <v>-0.0115</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4994</v>
@@ -1078,13 +1078,13 @@
         <v>0.3895</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6244</v>
+        <v>-0.1862</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3092</v>
+        <v>-0.0101</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3152</v>
+        <v>-0.1761</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9729</v>
+        <v>-3.4048</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4022</v>
+        <v>-2.9177</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5707</v>
+        <v>-0.4872</v>
       </c>
       <c r="G9" t="n">
         <v>-3.0091</v>
@@ -1156,13 +1156,13 @@
         <v>1.9474</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5548</v>
+        <v>-0.9868</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0512</v>
+        <v>-0.5667</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5036</v>
+        <v>-0.4202</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3826</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.5216</v>
+        <v>-5.0873</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4735</v>
+        <v>-4.1504</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0482</v>
+        <v>-0.9369</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8524</v>
@@ -1234,13 +1234,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2797</v>
+        <v>-0.8454</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.6663</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2904</v>
+        <v>-0.1791</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.1124</v>
+        <v>-5.8512</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.425</v>
+        <v>-2.1638</v>
       </c>
       <c r="F11" t="n">
         <v>-3.6874</v>
@@ -1312,10 +1312,10 @@
         <v>0.3895</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9026</v>
+        <v>-0.6414</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.5427</v>
       </c>
       <c r="U11" t="n">
         <v>-0.0988</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-13.2206</v>
+        <v>-12.2467</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.1011</v>
+        <v>-10.1736</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1197</v>
+        <v>-2.0732</v>
       </c>
       <c r="G12" t="n">
         <v>-7.4671</v>
@@ -1366,7 +1366,7 @@
         <v>3.722399999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>5.486399999999999</v>
+        <v>5.486400000000001</v>
       </c>
       <c r="L12" t="n">
         <v>-1.764</v>
@@ -1390,13 +1390,13 @@
         <v>15.5789</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.4077</v>
+        <v>-7.4339</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.459099999999999</v>
+        <v>-4.5314</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.9489</v>
+        <v>-2.902699999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2141</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.5524</v>
+        <v>5.6615</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7982</v>
+        <v>4.9496</v>
       </c>
       <c r="F13" t="n">
-        <v>2.7542</v>
+        <v>0.7119</v>
       </c>
       <c r="G13" t="n">
-        <v>4.464</v>
+        <v>4.1101</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0985</v>
+        <v>-0.3263</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3655</v>
+        <v>4.4364</v>
       </c>
       <c r="J13" t="n">
-        <v>3.231</v>
+        <v>5.681</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0616</v>
+        <v>1.7499</v>
       </c>
       <c r="L13" t="n">
-        <v>3.1694</v>
+        <v>3.9311</v>
       </c>
       <c r="M13" t="n">
-        <v>1.233</v>
+        <v>-1.5709</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0369</v>
+        <v>-2.0763</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1961</v>
+        <v>0.5054</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.7789</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1684</v>
+        <v>-1.9474</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3895</v>
+        <v>1.5579</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6463</v>
+        <v>1.2642</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4854</v>
+        <v>0.6055</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1318</v>
+        <v>0.6587</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2211</v>
+        <v>0.6767</v>
       </c>
       <c r="W13" t="n">
-        <v>1.2211</v>
+        <v>0.6105</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7806</v>
+        <v>5.5778</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1522</v>
+        <v>3.2966</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6284</v>
+        <v>2.2812</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1101</v>
+        <v>4.464</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3263</v>
+        <v>0.0985</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4364</v>
+        <v>4.3655</v>
       </c>
       <c r="J14" t="n">
-        <v>5.681</v>
+        <v>3.231</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7499</v>
+        <v>0.0616</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9311</v>
+        <v>3.1694</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5709</v>
+        <v>1.233</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.0763</v>
+        <v>0.0369</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5054</v>
+        <v>1.1961</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3895</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9474</v>
+        <v>-1.1684</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5579</v>
+        <v>0.3895</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3833</v>
+        <v>0.6716</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.192</v>
+        <v>0.0129</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5752</v>
+        <v>0.6587</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6767</v>
+        <v>1.2211</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6105</v>
+        <v>1.2211</v>
       </c>
       <c r="X14" t="n">
-        <v>0.06619999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>M. LORENZO SALCEDA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9851</v>
+        <v>3.8079</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4197</v>
+        <v>2.6631</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5654</v>
+        <v>1.1448</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.1545</v>
+        <v>2.1204</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.2838</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1293</v>
+        <v>2.6259</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2046</v>
+        <v>2.3742</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3667</v>
+        <v>0.2668</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1621</v>
+        <v>2.1074</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9499</v>
+        <v>-0.2539</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9171</v>
+        <v>-0.7723</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0328</v>
+        <v>0.5185</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3895</v>
+        <v>0.7789</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5579</v>
+        <v>0.7789</v>
       </c>
       <c r="S15" t="n">
-        <v>3.9623</v>
+        <v>0.8424</v>
       </c>
       <c r="T15" t="n">
-        <v>3.7333</v>
+        <v>0.2889</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2291</v>
+        <v>0.5535</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5667</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8384</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.06619999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. LORENZO SALCEDA</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1264</v>
+        <v>2.7029</v>
       </c>
       <c r="E16" t="n">
-        <v>2.065</v>
+        <v>1.5248</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0613</v>
+        <v>1.1781</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1204</v>
+        <v>1.4801</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.6259</v>
+        <v>0.6287</v>
       </c>
       <c r="J16" t="n">
-        <v>2.3742</v>
+        <v>1.2747</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2668</v>
+        <v>1.0315</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1074</v>
+        <v>0.2432</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2539</v>
+        <v>0.2054</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7723</v>
+        <v>-0.1802</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5185</v>
+        <v>0.3856</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7789</v>
+        <v>0.3895</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7789</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1609</v>
+        <v>1.1128</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3092</v>
+        <v>0.4449</v>
       </c>
       <c r="U16" t="n">
-        <v>0.47</v>
+        <v>0.6679</v>
       </c>
       <c r="V16" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2795</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.06619999999999999</v>
+        <v>-0.2795</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9068</v>
+        <v>1.5821</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9235</v>
+        <v>-0.1719</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9833</v>
+        <v>1.7539</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4801</v>
+        <v>-1.1545</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8512999999999999</v>
+        <v>-1.2838</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6287</v>
+        <v>0.1293</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2747</v>
+        <v>-0.2046</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0315</v>
+        <v>-0.3667</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2432</v>
+        <v>0.1621</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2054</v>
+        <v>-0.9499</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1802</v>
+        <v>-0.9171</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3856</v>
+        <v>-0.0328</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3895</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1947</v>
+        <v>-1.9474</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.5579</v>
       </c>
       <c r="S17" t="n">
-        <v>1.3167</v>
+        <v>1.5593</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8436</v>
+        <v>1.1417</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4732</v>
+        <v>0.4176</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2795</v>
+        <v>1.5667</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.8384</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2795</v>
+        <v>0.7282999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2023</v>
+        <v>1.5648</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2513</v>
+        <v>-0.7497</v>
       </c>
       <c r="F18" t="n">
-        <v>2.4537</v>
+        <v>2.3145</v>
       </c>
       <c r="G18" t="n">
         <v>0.725</v>
@@ -1858,13 +1858,13 @@
         <v>1.3632</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5796</v>
+        <v>0.9421</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9054</v>
+        <v>0.407</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6742</v>
+        <v>0.535</v>
       </c>
       <c r="V18" t="n">
         <v>0.6767</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7511</v>
+        <v>1.4281</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5616</v>
+        <v>0.9603</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1895</v>
+        <v>0.4677</v>
       </c>
       <c r="G19" t="n">
         <v>2.2321</v>
@@ -1936,13 +1936,13 @@
         <v>0.7789</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2132</v>
+        <v>0.8902</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0064</v>
+        <v>0.3923</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2196</v>
+        <v>0.4979</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3311</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5996</v>
+        <v>0.1087</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0192</v>
+        <v>0.0805</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6188</v>
+        <v>0.0282</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0481</v>
@@ -2014,13 +2014,13 @@
         <v>0.7789</v>
       </c>
       <c r="S20" t="n">
-        <v>1.453</v>
+        <v>0.9621</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0683</v>
+        <v>0.0314</v>
       </c>
       <c r="U20" t="n">
-        <v>1.5213</v>
+        <v>0.9307</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6105</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.6558</v>
+        <v>-1.3721</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9256</v>
+        <v>-3.0253</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2699</v>
+        <v>1.6532</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3441</v>
@@ -2092,13 +2092,13 @@
         <v>0.5842000000000001</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0001</v>
+        <v>0.2836</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0064</v>
+        <v>-0.1061</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0064</v>
+        <v>0.3897</v>
       </c>
       <c r="V21" t="n">
         <v>1.2726</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2375</v>
+        <v>-3.4555</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9237</v>
+        <v>-2.525</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3138</v>
+        <v>-0.9305</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9395</v>
@@ -2170,13 +2170,13 @@
         <v>0.9737</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7975</v>
+        <v>-0.0155</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.671</v>
+        <v>-0.2722</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1265</v>
+        <v>0.2568</v>
       </c>
       <c r="V22" t="n">
         <v>-1.5005</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7904</v>
+        <v>-3.721</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.681</v>
+        <v>-4.8835</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8905</v>
+        <v>1.1626</v>
       </c>
       <c r="G23" t="n">
         <v>-2.1783</v>
@@ -2248,13 +2248,13 @@
         <v>1.3632</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5099</v>
+        <v>0.5595</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7946</v>
+        <v>0.0028</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2847</v>
+        <v>0.5567</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5443</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>13.2206</v>
+        <v>13.8852</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1194</v>
+        <v>2.1195</v>
       </c>
       <c r="F24" t="n">
-        <v>11.1012</v>
+        <v>11.7656</v>
       </c>
       <c r="G24" t="n">
         <v>7.4672</v>
@@ -2305,7 +2305,7 @@
         <v>6.874499999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>4.315100000000002</v>
+        <v>4.3151</v>
       </c>
       <c r="M24" t="n">
         <v>-3.7224</v>
@@ -2326,16 +2326,16 @@
         <v>10.7105</v>
       </c>
       <c r="S24" t="n">
-        <v>8.4078</v>
+        <v>9.0723</v>
       </c>
       <c r="T24" t="n">
-        <v>2.948999999999999</v>
+        <v>2.9491</v>
       </c>
       <c r="U24" t="n">
-        <v>5.459</v>
+        <v>6.123200000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>2.214100000000001</v>
+        <v>2.2141</v>
       </c>
       <c r="W24" t="n">
         <v>3.5599</v>
